--- a/examples/results/Tryptophan_design_results_ecFactory_fcc_result.xlsx
+++ b/examples/results/Tryptophan_design_results_ecFactory_fcc_result.xlsx
@@ -429,6 +429,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0</t>
+        </is>
+      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>gene_name</t>
@@ -466,7 +471,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>b2551</t>
         </is>
@@ -487,14 +492,14 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-6.341744809821215e-15</v>
+        <v>2.001613205599821e-14</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>b0529</t>
         </is>
@@ -515,14 +520,14 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-8.948796465233656e-13</v>
+        <v>1.240603828421275e-13</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>b1852</t>
         </is>
@@ -543,14 +548,14 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>5.202212539306466e-15</v>
+        <v>-7.927181012276519e-16</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>b0767</t>
         </is>
@@ -571,42 +576,42 @@
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.2500000000000001</v>
+        <v>8.820970671410697e-13</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>b2029</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>0.1824571256088911</v>
+        <v>1000</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>OE</t>
         </is>
       </c>
       <c r="E6" t="n">
         <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.2438761579269342</v>
+        <v>1.940177552754678e-13</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>b0008</t>
         </is>
@@ -629,14 +634,14 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>4.77117207176393e-14</v>
+        <v>1.9580137100323e-13</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2313414272383159</v>
+        <v>-0.2316690486513085</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>b2464</t>
         </is>
@@ -659,14 +664,14 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>4.850443881886695e-14</v>
+        <v>1.940177552754678e-13</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>b2906</t>
         </is>
@@ -687,14 +692,14 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7498940131581511</v>
+        <v>0.9999999999999957</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>b3867</t>
         </is>
@@ -715,14 +720,14 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>3.765410980831347e-15</v>
+        <v>-1.98179525306913e-16</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>b3125</t>
         </is>
@@ -743,14 +748,14 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.93702056504845e-13</v>
+        <v>-1.298868608861508e-12</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>b1033</t>
         </is>
@@ -771,14 +776,14 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>4.850443881886695e-14</v>
+        <v>1.940177552754678e-13</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>b0508</t>
         </is>
@@ -799,14 +804,14 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>9.215347926771453e-15</v>
+        <v>-3.408687835278903e-14</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>b0509</t>
         </is>
@@ -827,14 +832,14 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>4.850443881886695e-14</v>
+        <v>1.940177552754678e-13</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>b3553</t>
         </is>
@@ -855,14 +860,14 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>8.120406049450759e-14</v>
+        <v>1.288166914494934e-14</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.25</v>
+        <v>-0.05034215391138917</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>b1199</t>
         </is>
@@ -883,14 +888,14 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>4.984215061468861e-14</v>
+        <v>1.93938483465345e-12</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.1160803467940846</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>b1200</t>
         </is>
@@ -911,14 +916,14 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>3.864500743484803e-15</v>
+        <v>3.96359050613826e-16</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1160803467939918</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>b3946</t>
         </is>
@@ -939,14 +944,14 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>4.850443881886695e-14</v>
+        <v>1.940177552754678e-13</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>b1198</t>
         </is>
@@ -967,14 +972,14 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.506164392332539e-14</v>
+        <v>1.583454407202235e-13</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1160803467940041</v>
+        <v>-0.04187215185690053</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>b0825</t>
         </is>
@@ -995,10 +1000,10 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>8.224945749050156e-13</v>
+        <v>3.099725955325426e-12</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
   </sheetData>
